--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -4046,10 +4046,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113237051</v>
+        <v>113237063</v>
       </c>
       <c r="B31" t="n">
-        <v>78697</v>
+        <v>91329</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306130</v>
+        <v>306029</v>
       </c>
       <c r="R31" t="n">
-        <v>6525370</v>
+        <v>6525415</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4122,6 +4122,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4148,10 +4153,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113237048</v>
+        <v>113237047</v>
       </c>
       <c r="B32" t="n">
-        <v>78697</v>
+        <v>90210</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4164,21 +4169,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>1588</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4188,10 +4193,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306201</v>
+        <v>306220</v>
       </c>
       <c r="R32" t="n">
-        <v>6525441</v>
+        <v>6525488</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4250,10 +4255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113237050</v>
+        <v>113237065</v>
       </c>
       <c r="B33" t="n">
-        <v>78697</v>
+        <v>91306</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4262,25 +4267,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4290,10 +4295,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306218</v>
+        <v>306104</v>
       </c>
       <c r="R33" t="n">
-        <v>6525455</v>
+        <v>6525382</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4326,6 +4331,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4352,10 +4362,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113237063</v>
+        <v>113237048</v>
       </c>
       <c r="B34" t="n">
-        <v>91313</v>
+        <v>78713</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4368,21 +4378,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4392,10 +4402,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306029</v>
+        <v>306201</v>
       </c>
       <c r="R34" t="n">
-        <v>6525415</v>
+        <v>6525441</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4428,11 +4438,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4459,10 +4464,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113237054</v>
+        <v>113237046</v>
       </c>
       <c r="B35" t="n">
-        <v>56765</v>
+        <v>90210</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4475,21 +4480,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4499,10 +4504,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306149</v>
+        <v>306234</v>
       </c>
       <c r="R35" t="n">
-        <v>6525175</v>
+        <v>6525467</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4535,11 +4540,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4566,10 +4566,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113237046</v>
+        <v>113237057</v>
       </c>
       <c r="B36" t="n">
-        <v>90194</v>
+        <v>56781</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4582,21 +4582,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1588</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306234</v>
+        <v>306222</v>
       </c>
       <c r="R36" t="n">
-        <v>6525467</v>
+        <v>6525470</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4642,6 +4642,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4668,10 +4673,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113237055</v>
+        <v>113237061</v>
       </c>
       <c r="B37" t="n">
-        <v>56781</v>
+        <v>96277</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4680,25 +4685,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4708,10 +4713,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306208</v>
+        <v>306100</v>
       </c>
       <c r="R37" t="n">
-        <v>6525440</v>
+        <v>6525128</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4744,11 +4749,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4775,10 +4775,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113237047</v>
+        <v>113237051</v>
       </c>
       <c r="B38" t="n">
-        <v>90194</v>
+        <v>78713</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4791,21 +4791,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1588</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306220</v>
+        <v>306130</v>
       </c>
       <c r="R38" t="n">
-        <v>6525488</v>
+        <v>6525370</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113237057</v>
+        <v>113237049</v>
       </c>
       <c r="B39" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4893,21 +4893,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306222</v>
+        <v>306210</v>
       </c>
       <c r="R39" t="n">
-        <v>6525470</v>
+        <v>6525458</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4953,11 +4953,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4984,10 +4979,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113237061</v>
+        <v>113237050</v>
       </c>
       <c r="B40" t="n">
-        <v>96261</v>
+        <v>78713</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4996,25 +4991,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5024,10 +5019,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306100</v>
+        <v>306218</v>
       </c>
       <c r="R40" t="n">
-        <v>6525128</v>
+        <v>6525455</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5086,10 +5081,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113237065</v>
+        <v>113237055</v>
       </c>
       <c r="B41" t="n">
-        <v>91290</v>
+        <v>56781</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5098,25 +5093,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5126,10 +5121,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306104</v>
+        <v>306208</v>
       </c>
       <c r="R41" t="n">
-        <v>6525382</v>
+        <v>6525440</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5166,7 +5161,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>5 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5193,10 +5188,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113237049</v>
+        <v>113237054</v>
       </c>
       <c r="B42" t="n">
-        <v>78697</v>
+        <v>56765</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5209,21 +5204,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5233,10 +5228,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306210</v>
+        <v>306149</v>
       </c>
       <c r="R42" t="n">
-        <v>6525458</v>
+        <v>6525175</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5269,6 +5264,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -4153,10 +4153,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113237047</v>
+        <v>113237065</v>
       </c>
       <c r="B32" t="n">
-        <v>90210</v>
+        <v>91306</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4165,25 +4165,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1588</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306220</v>
+        <v>306104</v>
       </c>
       <c r="R32" t="n">
-        <v>6525488</v>
+        <v>6525382</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4229,6 +4229,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,10 +4260,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113237065</v>
+        <v>113237048</v>
       </c>
       <c r="B33" t="n">
-        <v>91306</v>
+        <v>78713</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4267,25 +4272,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4295,10 +4300,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306104</v>
+        <v>306201</v>
       </c>
       <c r="R33" t="n">
-        <v>6525382</v>
+        <v>6525441</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4331,11 +4336,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4362,10 +4362,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113237048</v>
+        <v>113237047</v>
       </c>
       <c r="B34" t="n">
-        <v>78713</v>
+        <v>90210</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4378,21 +4378,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>1588</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306201</v>
+        <v>306220</v>
       </c>
       <c r="R34" t="n">
-        <v>6525441</v>
+        <v>6525488</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4464,10 +4464,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113237046</v>
+        <v>113237057</v>
       </c>
       <c r="B35" t="n">
-        <v>90210</v>
+        <v>56781</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4480,21 +4480,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1588</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306234</v>
+        <v>306222</v>
       </c>
       <c r="R35" t="n">
-        <v>6525467</v>
+        <v>6525470</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4540,6 +4540,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4566,10 +4571,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113237057</v>
+        <v>113237046</v>
       </c>
       <c r="B36" t="n">
-        <v>56781</v>
+        <v>90210</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4582,21 +4587,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>1588</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306222</v>
+        <v>306234</v>
       </c>
       <c r="R36" t="n">
-        <v>6525470</v>
+        <v>6525467</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4642,11 +4647,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -4046,10 +4046,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113237063</v>
+        <v>113237048</v>
       </c>
       <c r="B31" t="n">
-        <v>91329</v>
+        <v>78713</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306029</v>
+        <v>306201</v>
       </c>
       <c r="R31" t="n">
-        <v>6525415</v>
+        <v>6525441</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4122,11 +4122,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4153,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113237065</v>
+        <v>113237054</v>
       </c>
       <c r="B32" t="n">
-        <v>91306</v>
+        <v>56765</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4165,25 +4160,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4193,10 +4188,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306104</v>
+        <v>306149</v>
       </c>
       <c r="R32" t="n">
-        <v>6525382</v>
+        <v>6525175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4233,7 +4228,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>5 fruktkroppar</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4260,10 +4255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113237048</v>
+        <v>113237063</v>
       </c>
       <c r="B33" t="n">
-        <v>78713</v>
+        <v>91329</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4276,21 +4271,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4300,10 +4295,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306201</v>
+        <v>306029</v>
       </c>
       <c r="R33" t="n">
-        <v>6525441</v>
+        <v>6525415</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4336,6 +4331,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4464,10 +4464,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113237057</v>
+        <v>113237051</v>
       </c>
       <c r="B35" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4480,21 +4480,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306222</v>
+        <v>306130</v>
       </c>
       <c r="R35" t="n">
-        <v>6525470</v>
+        <v>6525370</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4540,11 +4540,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4571,10 +4566,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113237046</v>
+        <v>113237057</v>
       </c>
       <c r="B36" t="n">
-        <v>90210</v>
+        <v>56781</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4587,21 +4582,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1588</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306234</v>
+        <v>306222</v>
       </c>
       <c r="R36" t="n">
-        <v>6525467</v>
+        <v>6525470</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4647,6 +4642,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4673,10 +4673,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113237061</v>
+        <v>113237046</v>
       </c>
       <c r="B37" t="n">
-        <v>96277</v>
+        <v>90210</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4685,25 +4685,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>1588</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306100</v>
+        <v>306234</v>
       </c>
       <c r="R37" t="n">
-        <v>6525128</v>
+        <v>6525467</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113237051</v>
+        <v>113237065</v>
       </c>
       <c r="B38" t="n">
-        <v>78713</v>
+        <v>91306</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4787,25 +4787,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306130</v>
+        <v>306104</v>
       </c>
       <c r="R38" t="n">
-        <v>6525370</v>
+        <v>6525382</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4851,6 +4851,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4877,10 +4882,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113237049</v>
+        <v>113237055</v>
       </c>
       <c r="B39" t="n">
-        <v>78713</v>
+        <v>56781</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4893,21 +4898,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4917,10 +4922,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306210</v>
+        <v>306208</v>
       </c>
       <c r="R39" t="n">
-        <v>6525458</v>
+        <v>6525440</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4953,6 +4958,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5081,10 +5091,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113237055</v>
+        <v>113237061</v>
       </c>
       <c r="B41" t="n">
-        <v>56781</v>
+        <v>96277</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5093,25 +5103,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5121,10 +5131,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306208</v>
+        <v>306100</v>
       </c>
       <c r="R41" t="n">
-        <v>6525440</v>
+        <v>6525128</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5157,11 +5167,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5188,10 +5193,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113237054</v>
+        <v>113237049</v>
       </c>
       <c r="B42" t="n">
-        <v>56765</v>
+        <v>78713</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5204,21 +5209,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5228,10 +5233,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306149</v>
+        <v>306210</v>
       </c>
       <c r="R42" t="n">
-        <v>6525175</v>
+        <v>6525458</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5264,11 +5269,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -4046,10 +4046,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113237048</v>
+        <v>113237047</v>
       </c>
       <c r="B31" t="n">
-        <v>78713</v>
+        <v>90222</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>1588</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306201</v>
+        <v>306220</v>
       </c>
       <c r="R31" t="n">
-        <v>6525441</v>
+        <v>6525488</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113237054</v>
+        <v>113237057</v>
       </c>
       <c r="B32" t="n">
-        <v>56765</v>
+        <v>56782</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4164,16 +4164,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306149</v>
+        <v>306222</v>
       </c>
       <c r="R32" t="n">
-        <v>6525175</v>
+        <v>6525470</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,10 +4255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113237063</v>
+        <v>113237061</v>
       </c>
       <c r="B33" t="n">
-        <v>91329</v>
+        <v>96289</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4267,25 +4267,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306029</v>
+        <v>306100</v>
       </c>
       <c r="R33" t="n">
-        <v>6525415</v>
+        <v>6525128</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4331,11 +4331,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4362,10 +4357,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113237047</v>
+        <v>113237046</v>
       </c>
       <c r="B34" t="n">
-        <v>90210</v>
+        <v>90222</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4402,10 +4397,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306220</v>
+        <v>306234</v>
       </c>
       <c r="R34" t="n">
-        <v>6525488</v>
+        <v>6525467</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4467,7 +4462,7 @@
         <v>113237051</v>
       </c>
       <c r="B35" t="n">
-        <v>78713</v>
+        <v>78725</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4566,10 +4561,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113237057</v>
+        <v>113237063</v>
       </c>
       <c r="B36" t="n">
-        <v>56781</v>
+        <v>91341</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4582,21 +4577,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4606,10 +4601,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306222</v>
+        <v>306029</v>
       </c>
       <c r="R36" t="n">
-        <v>6525470</v>
+        <v>6525415</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4646,7 +4641,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4673,10 +4668,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113237046</v>
+        <v>113237065</v>
       </c>
       <c r="B37" t="n">
-        <v>90210</v>
+        <v>91318</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4685,25 +4680,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1588</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4713,10 +4708,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306234</v>
+        <v>306104</v>
       </c>
       <c r="R37" t="n">
-        <v>6525467</v>
+        <v>6525382</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4749,6 +4744,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4775,10 +4775,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113237065</v>
+        <v>113237055</v>
       </c>
       <c r="B38" t="n">
-        <v>91306</v>
+        <v>56782</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4787,25 +4787,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306104</v>
+        <v>306208</v>
       </c>
       <c r="R38" t="n">
-        <v>6525382</v>
+        <v>6525440</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>5 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4882,10 +4882,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113237055</v>
+        <v>113237054</v>
       </c>
       <c r="B39" t="n">
-        <v>56781</v>
+        <v>56766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306208</v>
+        <v>306149</v>
       </c>
       <c r="R39" t="n">
-        <v>6525440</v>
+        <v>6525175</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4989,10 +4989,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113237050</v>
+        <v>113237048</v>
       </c>
       <c r="B40" t="n">
-        <v>78713</v>
+        <v>78725</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306218</v>
+        <v>306201</v>
       </c>
       <c r="R40" t="n">
-        <v>6525455</v>
+        <v>6525441</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5091,10 +5091,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113237061</v>
+        <v>113237050</v>
       </c>
       <c r="B41" t="n">
-        <v>96277</v>
+        <v>78725</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5103,25 +5103,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306100</v>
+        <v>306218</v>
       </c>
       <c r="R41" t="n">
-        <v>6525128</v>
+        <v>6525455</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
         <v>113237049</v>
       </c>
       <c r="B42" t="n">
-        <v>78713</v>
+        <v>78725</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -4046,10 +4046,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113237047</v>
+        <v>113237061</v>
       </c>
       <c r="B31" t="n">
-        <v>90222</v>
+        <v>96289</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4058,25 +4058,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1588</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306220</v>
+        <v>306100</v>
       </c>
       <c r="R31" t="n">
-        <v>6525488</v>
+        <v>6525128</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113237057</v>
+        <v>113237054</v>
       </c>
       <c r="B32" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4164,16 +4164,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306222</v>
+        <v>306149</v>
       </c>
       <c r="R32" t="n">
-        <v>6525470</v>
+        <v>6525175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,10 +4255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113237061</v>
+        <v>113237047</v>
       </c>
       <c r="B33" t="n">
-        <v>96289</v>
+        <v>90222</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4267,25 +4267,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>1588</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306100</v>
+        <v>306220</v>
       </c>
       <c r="R33" t="n">
-        <v>6525128</v>
+        <v>6525488</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4357,10 +4357,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113237046</v>
+        <v>113237048</v>
       </c>
       <c r="B34" t="n">
-        <v>90222</v>
+        <v>78725</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4373,21 +4373,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1588</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306234</v>
+        <v>306201</v>
       </c>
       <c r="R34" t="n">
-        <v>6525467</v>
+        <v>6525441</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4459,10 +4459,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113237051</v>
+        <v>113237065</v>
       </c>
       <c r="B35" t="n">
-        <v>78725</v>
+        <v>91318</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4471,25 +4471,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306130</v>
+        <v>306104</v>
       </c>
       <c r="R35" t="n">
-        <v>6525370</v>
+        <v>6525382</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4535,6 +4535,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4561,10 +4566,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113237063</v>
+        <v>113237049</v>
       </c>
       <c r="B36" t="n">
-        <v>91341</v>
+        <v>78725</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4577,21 +4582,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4601,10 +4606,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306029</v>
+        <v>306210</v>
       </c>
       <c r="R36" t="n">
-        <v>6525415</v>
+        <v>6525458</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4637,11 +4642,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4668,10 +4668,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113237065</v>
+        <v>113237055</v>
       </c>
       <c r="B37" t="n">
-        <v>91318</v>
+        <v>56782</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4680,25 +4680,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306104</v>
+        <v>306208</v>
       </c>
       <c r="R37" t="n">
-        <v>6525382</v>
+        <v>6525440</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>5 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4775,7 +4775,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113237055</v>
+        <v>113237057</v>
       </c>
       <c r="B38" t="n">
         <v>56782</v>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306208</v>
+        <v>306222</v>
       </c>
       <c r="R38" t="n">
-        <v>6525440</v>
+        <v>6525470</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4882,10 +4882,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113237054</v>
+        <v>113237051</v>
       </c>
       <c r="B39" t="n">
-        <v>56766</v>
+        <v>78725</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4898,21 +4898,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306149</v>
+        <v>306130</v>
       </c>
       <c r="R39" t="n">
-        <v>6525175</v>
+        <v>6525370</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4958,11 +4958,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4989,7 +4984,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113237048</v>
+        <v>113237050</v>
       </c>
       <c r="B40" t="n">
         <v>78725</v>
@@ -5029,10 +5024,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306201</v>
+        <v>306218</v>
       </c>
       <c r="R40" t="n">
-        <v>6525441</v>
+        <v>6525455</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5091,10 +5086,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113237050</v>
+        <v>113237063</v>
       </c>
       <c r="B41" t="n">
-        <v>78725</v>
+        <v>91341</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5107,21 +5102,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5131,10 +5126,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306218</v>
+        <v>306029</v>
       </c>
       <c r="R41" t="n">
-        <v>6525455</v>
+        <v>6525415</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5167,6 +5162,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5193,10 +5193,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113237049</v>
+        <v>113237046</v>
       </c>
       <c r="B42" t="n">
-        <v>78725</v>
+        <v>90222</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5209,21 +5209,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>1588</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306210</v>
+        <v>306234</v>
       </c>
       <c r="R42" t="n">
-        <v>6525458</v>
+        <v>6525467</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -4148,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113237054</v>
+        <v>113237047</v>
       </c>
       <c r="B32" t="n">
-        <v>56766</v>
+        <v>90222</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4164,21 +4164,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306149</v>
+        <v>306220</v>
       </c>
       <c r="R32" t="n">
-        <v>6525175</v>
+        <v>6525488</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4224,11 +4224,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,10 +4250,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113237047</v>
+        <v>113237054</v>
       </c>
       <c r="B33" t="n">
-        <v>90222</v>
+        <v>56766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4271,21 +4266,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4295,10 +4290,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306220</v>
+        <v>306149</v>
       </c>
       <c r="R33" t="n">
-        <v>6525488</v>
+        <v>6525175</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4331,6 +4326,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4566,10 +4566,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113237049</v>
+        <v>113237055</v>
       </c>
       <c r="B36" t="n">
-        <v>78725</v>
+        <v>56782</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4582,21 +4582,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306210</v>
+        <v>306208</v>
       </c>
       <c r="R36" t="n">
-        <v>6525458</v>
+        <v>6525440</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4642,6 +4642,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4668,10 +4673,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113237055</v>
+        <v>113237049</v>
       </c>
       <c r="B37" t="n">
-        <v>56782</v>
+        <v>78725</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4684,21 +4689,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4708,10 +4713,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306208</v>
+        <v>306210</v>
       </c>
       <c r="R37" t="n">
-        <v>6525440</v>
+        <v>6525458</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4744,11 +4749,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5086,10 +5086,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113237063</v>
+        <v>113237046</v>
       </c>
       <c r="B41" t="n">
-        <v>91341</v>
+        <v>90222</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5102,21 +5102,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>1588</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306029</v>
+        <v>306234</v>
       </c>
       <c r="R41" t="n">
-        <v>6525415</v>
+        <v>6525467</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5162,11 +5162,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5193,10 +5188,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113237046</v>
+        <v>113237063</v>
       </c>
       <c r="B42" t="n">
-        <v>90222</v>
+        <v>91341</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5209,21 +5204,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1588</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5233,10 +5228,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306234</v>
+        <v>306029</v>
       </c>
       <c r="R42" t="n">
-        <v>6525467</v>
+        <v>6525415</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5269,6 +5264,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -4046,10 +4046,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113237061</v>
+        <v>113237055</v>
       </c>
       <c r="B31" t="n">
-        <v>96289</v>
+        <v>56782</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4058,25 +4058,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306100</v>
+        <v>306208</v>
       </c>
       <c r="R31" t="n">
-        <v>6525128</v>
+        <v>6525440</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4122,6 +4122,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4148,10 +4153,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113237047</v>
+        <v>113237054</v>
       </c>
       <c r="B32" t="n">
-        <v>90222</v>
+        <v>56766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4164,21 +4169,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4188,10 +4193,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306220</v>
+        <v>306149</v>
       </c>
       <c r="R32" t="n">
-        <v>6525488</v>
+        <v>6525175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4224,6 +4229,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4250,10 +4260,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113237054</v>
+        <v>113237051</v>
       </c>
       <c r="B33" t="n">
-        <v>56766</v>
+        <v>78747</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4266,21 +4276,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4290,10 +4300,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306149</v>
+        <v>306130</v>
       </c>
       <c r="R33" t="n">
-        <v>6525175</v>
+        <v>6525370</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4326,11 +4336,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4357,10 +4362,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113237048</v>
+        <v>113237063</v>
       </c>
       <c r="B34" t="n">
-        <v>78725</v>
+        <v>91363</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4373,21 +4378,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4397,10 +4402,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306201</v>
+        <v>306029</v>
       </c>
       <c r="R34" t="n">
-        <v>6525441</v>
+        <v>6525415</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4433,6 +4438,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4459,10 +4469,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113237065</v>
+        <v>113237050</v>
       </c>
       <c r="B35" t="n">
-        <v>91318</v>
+        <v>78747</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4471,25 +4481,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4499,10 +4509,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306104</v>
+        <v>306218</v>
       </c>
       <c r="R35" t="n">
-        <v>6525382</v>
+        <v>6525455</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4535,11 +4545,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4566,10 +4571,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113237055</v>
+        <v>113237046</v>
       </c>
       <c r="B36" t="n">
-        <v>56782</v>
+        <v>90244</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4582,21 +4587,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>1588</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306208</v>
+        <v>306234</v>
       </c>
       <c r="R36" t="n">
-        <v>6525440</v>
+        <v>6525467</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4642,11 +4647,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4673,10 +4673,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113237049</v>
+        <v>113237057</v>
       </c>
       <c r="B37" t="n">
-        <v>78725</v>
+        <v>56782</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4689,21 +4689,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306210</v>
+        <v>306222</v>
       </c>
       <c r="R37" t="n">
-        <v>6525458</v>
+        <v>6525470</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4749,6 +4749,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4775,10 +4780,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113237057</v>
+        <v>113237061</v>
       </c>
       <c r="B38" t="n">
-        <v>56782</v>
+        <v>96311</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4787,25 +4792,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4815,10 +4820,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306222</v>
+        <v>306100</v>
       </c>
       <c r="R38" t="n">
-        <v>6525470</v>
+        <v>6525128</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4851,11 +4856,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4882,10 +4882,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113237051</v>
+        <v>113237047</v>
       </c>
       <c r="B39" t="n">
-        <v>78725</v>
+        <v>90244</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4898,21 +4898,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>1588</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306130</v>
+        <v>306220</v>
       </c>
       <c r="R39" t="n">
-        <v>6525370</v>
+        <v>6525488</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113237050</v>
+        <v>113237049</v>
       </c>
       <c r="B40" t="n">
-        <v>78725</v>
+        <v>78747</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306218</v>
+        <v>306210</v>
       </c>
       <c r="R40" t="n">
-        <v>6525455</v>
+        <v>6525458</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5086,10 +5086,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113237046</v>
+        <v>113237065</v>
       </c>
       <c r="B41" t="n">
-        <v>90222</v>
+        <v>91340</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5098,25 +5098,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1588</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306234</v>
+        <v>306104</v>
       </c>
       <c r="R41" t="n">
-        <v>6525467</v>
+        <v>6525382</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5162,6 +5162,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5188,10 +5193,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113237063</v>
+        <v>113237048</v>
       </c>
       <c r="B42" t="n">
-        <v>91341</v>
+        <v>78747</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5204,21 +5209,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5228,10 +5233,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306029</v>
+        <v>306201</v>
       </c>
       <c r="R42" t="n">
-        <v>6525415</v>
+        <v>6525441</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5264,11 +5269,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -4046,10 +4046,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113237055</v>
+        <v>113237049</v>
       </c>
       <c r="B31" t="n">
-        <v>56782</v>
+        <v>78751</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306208</v>
+        <v>306210</v>
       </c>
       <c r="R31" t="n">
-        <v>6525440</v>
+        <v>6525458</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4122,11 +4122,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4153,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113237054</v>
+        <v>113237057</v>
       </c>
       <c r="B32" t="n">
-        <v>56766</v>
+        <v>56785</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4169,16 +4164,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4193,10 +4188,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306149</v>
+        <v>306222</v>
       </c>
       <c r="R32" t="n">
-        <v>6525175</v>
+        <v>6525470</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4233,7 +4228,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4260,10 +4255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113237051</v>
+        <v>113237050</v>
       </c>
       <c r="B33" t="n">
-        <v>78747</v>
+        <v>78751</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4300,10 +4295,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306130</v>
+        <v>306218</v>
       </c>
       <c r="R33" t="n">
-        <v>6525370</v>
+        <v>6525455</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4365,7 +4360,7 @@
         <v>113237063</v>
       </c>
       <c r="B34" t="n">
-        <v>91363</v>
+        <v>91367</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4469,10 +4464,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113237050</v>
+        <v>113237051</v>
       </c>
       <c r="B35" t="n">
-        <v>78747</v>
+        <v>78751</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4509,10 +4504,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306218</v>
+        <v>306130</v>
       </c>
       <c r="R35" t="n">
-        <v>6525455</v>
+        <v>6525370</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4571,10 +4566,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113237046</v>
+        <v>113237047</v>
       </c>
       <c r="B36" t="n">
-        <v>90244</v>
+        <v>90248</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306234</v>
+        <v>306220</v>
       </c>
       <c r="R36" t="n">
-        <v>6525467</v>
+        <v>6525488</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4673,10 +4668,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113237057</v>
+        <v>113237048</v>
       </c>
       <c r="B37" t="n">
-        <v>56782</v>
+        <v>78751</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4689,21 +4684,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4713,10 +4708,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306222</v>
+        <v>306201</v>
       </c>
       <c r="R37" t="n">
-        <v>6525470</v>
+        <v>6525441</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4749,11 +4744,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4780,10 +4770,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113237061</v>
+        <v>113237054</v>
       </c>
       <c r="B38" t="n">
-        <v>96311</v>
+        <v>56769</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4792,25 +4782,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4820,10 +4810,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306100</v>
+        <v>306149</v>
       </c>
       <c r="R38" t="n">
-        <v>6525128</v>
+        <v>6525175</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4856,6 +4846,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4882,10 +4877,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113237047</v>
+        <v>113237061</v>
       </c>
       <c r="B39" t="n">
-        <v>90244</v>
+        <v>96315</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4894,25 +4889,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1588</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4922,10 +4917,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306220</v>
+        <v>306100</v>
       </c>
       <c r="R39" t="n">
-        <v>6525488</v>
+        <v>6525128</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4984,10 +4979,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113237049</v>
+        <v>113237046</v>
       </c>
       <c r="B40" t="n">
-        <v>78747</v>
+        <v>90248</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5000,21 +4995,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>1588</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5024,10 +5019,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306210</v>
+        <v>306234</v>
       </c>
       <c r="R40" t="n">
-        <v>6525458</v>
+        <v>6525467</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5086,10 +5081,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113237065</v>
+        <v>113237055</v>
       </c>
       <c r="B41" t="n">
-        <v>91340</v>
+        <v>56785</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5098,25 +5093,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5126,10 +5121,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306104</v>
+        <v>306208</v>
       </c>
       <c r="R41" t="n">
-        <v>6525382</v>
+        <v>6525440</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5166,7 +5161,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>5 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5193,10 +5188,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113237048</v>
+        <v>113237065</v>
       </c>
       <c r="B42" t="n">
-        <v>78747</v>
+        <v>91344</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5205,25 +5200,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5233,10 +5228,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306201</v>
+        <v>306104</v>
       </c>
       <c r="R42" t="n">
-        <v>6525441</v>
+        <v>6525382</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5269,6 +5264,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -4148,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113237057</v>
+        <v>113237050</v>
       </c>
       <c r="B32" t="n">
-        <v>56785</v>
+        <v>78751</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4164,21 +4164,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306222</v>
+        <v>306218</v>
       </c>
       <c r="R32" t="n">
-        <v>6525470</v>
+        <v>6525455</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4224,11 +4224,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,10 +4250,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113237050</v>
+        <v>113237063</v>
       </c>
       <c r="B33" t="n">
-        <v>78751</v>
+        <v>91367</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4271,21 +4266,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4295,10 +4290,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306218</v>
+        <v>306029</v>
       </c>
       <c r="R33" t="n">
-        <v>6525455</v>
+        <v>6525415</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4331,6 +4326,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4357,10 +4357,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113237063</v>
+        <v>113237057</v>
       </c>
       <c r="B34" t="n">
-        <v>91367</v>
+        <v>56785</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4373,21 +4373,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306029</v>
+        <v>306222</v>
       </c>
       <c r="R34" t="n">
-        <v>6525415</v>
+        <v>6525470</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>2 fruktkroppar</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4877,10 +4877,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113237061</v>
+        <v>113237046</v>
       </c>
       <c r="B39" t="n">
-        <v>96315</v>
+        <v>90248</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4889,25 +4889,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>1588</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306100</v>
+        <v>306234</v>
       </c>
       <c r="R39" t="n">
-        <v>6525128</v>
+        <v>6525467</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4979,10 +4979,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113237046</v>
+        <v>113237055</v>
       </c>
       <c r="B40" t="n">
-        <v>90248</v>
+        <v>56785</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4995,21 +4995,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1588</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306234</v>
+        <v>306208</v>
       </c>
       <c r="R40" t="n">
-        <v>6525467</v>
+        <v>6525440</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5055,6 +5055,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5081,10 +5086,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113237055</v>
+        <v>113237061</v>
       </c>
       <c r="B41" t="n">
-        <v>56785</v>
+        <v>96315</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5093,25 +5098,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5121,10 +5126,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306208</v>
+        <v>306100</v>
       </c>
       <c r="R41" t="n">
-        <v>6525440</v>
+        <v>6525128</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5157,11 +5162,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -4046,7 +4046,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113237049</v>
+        <v>113237048</v>
       </c>
       <c r="B31" t="n">
         <v>78751</v>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306210</v>
+        <v>306201</v>
       </c>
       <c r="R31" t="n">
-        <v>6525458</v>
+        <v>6525441</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113237050</v>
+        <v>113237057</v>
       </c>
       <c r="B32" t="n">
-        <v>78751</v>
+        <v>56785</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4164,21 +4164,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306218</v>
+        <v>306222</v>
       </c>
       <c r="R32" t="n">
-        <v>6525455</v>
+        <v>6525470</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4224,6 +4224,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4250,10 +4255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113237063</v>
+        <v>113237050</v>
       </c>
       <c r="B33" t="n">
-        <v>91367</v>
+        <v>78751</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4266,21 +4271,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4290,10 +4295,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306029</v>
+        <v>306218</v>
       </c>
       <c r="R33" t="n">
-        <v>6525415</v>
+        <v>6525455</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4326,11 +4331,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4357,10 +4357,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113237057</v>
+        <v>113237061</v>
       </c>
       <c r="B34" t="n">
-        <v>56785</v>
+        <v>96315</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4369,25 +4369,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306222</v>
+        <v>306100</v>
       </c>
       <c r="R34" t="n">
-        <v>6525470</v>
+        <v>6525128</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4433,11 +4433,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4464,10 +4459,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113237051</v>
+        <v>113237046</v>
       </c>
       <c r="B35" t="n">
-        <v>78751</v>
+        <v>90248</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4480,21 +4475,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>1588</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4504,10 +4499,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306130</v>
+        <v>306234</v>
       </c>
       <c r="R35" t="n">
-        <v>6525370</v>
+        <v>6525467</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4566,10 +4561,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113237047</v>
+        <v>113237055</v>
       </c>
       <c r="B36" t="n">
-        <v>90248</v>
+        <v>56785</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4582,21 +4577,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1588</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4606,10 +4601,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306220</v>
+        <v>306208</v>
       </c>
       <c r="R36" t="n">
-        <v>6525488</v>
+        <v>6525440</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4642,6 +4637,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4668,7 +4668,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113237048</v>
+        <v>113237049</v>
       </c>
       <c r="B37" t="n">
         <v>78751</v>
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306201</v>
+        <v>306210</v>
       </c>
       <c r="R37" t="n">
-        <v>6525441</v>
+        <v>6525458</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113237054</v>
+        <v>113237051</v>
       </c>
       <c r="B38" t="n">
-        <v>56769</v>
+        <v>78751</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4786,21 +4786,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306149</v>
+        <v>306130</v>
       </c>
       <c r="R38" t="n">
-        <v>6525175</v>
+        <v>6525370</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4846,11 +4846,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4877,10 +4872,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113237046</v>
+        <v>113237065</v>
       </c>
       <c r="B39" t="n">
-        <v>90248</v>
+        <v>91344</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4889,25 +4884,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1588</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4917,10 +4912,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306234</v>
+        <v>306104</v>
       </c>
       <c r="R39" t="n">
-        <v>6525467</v>
+        <v>6525382</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4953,6 +4948,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4979,10 +4979,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113237055</v>
+        <v>113237054</v>
       </c>
       <c r="B40" t="n">
-        <v>56785</v>
+        <v>56769</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306208</v>
+        <v>306149</v>
       </c>
       <c r="R40" t="n">
-        <v>6525440</v>
+        <v>6525175</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5086,10 +5086,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113237061</v>
+        <v>113237063</v>
       </c>
       <c r="B41" t="n">
-        <v>96315</v>
+        <v>91367</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5098,25 +5098,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306100</v>
+        <v>306029</v>
       </c>
       <c r="R41" t="n">
-        <v>6525128</v>
+        <v>6525415</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5162,6 +5162,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5188,10 +5193,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113237065</v>
+        <v>113237047</v>
       </c>
       <c r="B42" t="n">
-        <v>91344</v>
+        <v>90248</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5200,25 +5205,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>1588</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5228,10 +5233,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306104</v>
+        <v>306220</v>
       </c>
       <c r="R42" t="n">
-        <v>6525382</v>
+        <v>6525488</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5264,11 +5269,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -4046,10 +4046,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113237048</v>
+        <v>113237055</v>
       </c>
       <c r="B31" t="n">
-        <v>78751</v>
+        <v>56789</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306201</v>
+        <v>306208</v>
       </c>
       <c r="R31" t="n">
-        <v>6525441</v>
+        <v>6525440</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4122,6 +4122,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4148,10 +4153,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113237057</v>
+        <v>113237063</v>
       </c>
       <c r="B32" t="n">
-        <v>56785</v>
+        <v>91373</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4164,21 +4169,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4188,10 +4193,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306222</v>
+        <v>306029</v>
       </c>
       <c r="R32" t="n">
-        <v>6525470</v>
+        <v>6525415</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4228,7 +4233,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,10 +4260,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113237050</v>
+        <v>113237054</v>
       </c>
       <c r="B33" t="n">
-        <v>78751</v>
+        <v>56773</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4271,21 +4276,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4295,10 +4300,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306218</v>
+        <v>306149</v>
       </c>
       <c r="R33" t="n">
-        <v>6525455</v>
+        <v>6525175</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4331,6 +4336,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4360,7 +4370,7 @@
         <v>113237061</v>
       </c>
       <c r="B34" t="n">
-        <v>96315</v>
+        <v>96321</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4462,7 +4472,7 @@
         <v>113237046</v>
       </c>
       <c r="B35" t="n">
-        <v>90248</v>
+        <v>90254</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4561,10 +4571,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113237055</v>
+        <v>113237047</v>
       </c>
       <c r="B36" t="n">
-        <v>56785</v>
+        <v>90254</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4577,21 +4587,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>1588</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4601,10 +4611,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306208</v>
+        <v>306220</v>
       </c>
       <c r="R36" t="n">
-        <v>6525440</v>
+        <v>6525488</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4637,11 +4647,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4671,7 +4676,7 @@
         <v>113237049</v>
       </c>
       <c r="B37" t="n">
-        <v>78751</v>
+        <v>78757</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4773,7 +4778,7 @@
         <v>113237051</v>
       </c>
       <c r="B38" t="n">
-        <v>78751</v>
+        <v>78757</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4875,7 +4880,7 @@
         <v>113237065</v>
       </c>
       <c r="B39" t="n">
-        <v>91344</v>
+        <v>91350</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4979,10 +4984,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113237054</v>
+        <v>113237057</v>
       </c>
       <c r="B40" t="n">
-        <v>56769</v>
+        <v>56789</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4995,16 +5000,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5019,10 +5024,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306149</v>
+        <v>306222</v>
       </c>
       <c r="R40" t="n">
-        <v>6525175</v>
+        <v>6525470</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5059,7 +5064,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5086,10 +5091,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113237063</v>
+        <v>113237050</v>
       </c>
       <c r="B41" t="n">
-        <v>91367</v>
+        <v>78757</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5102,21 +5107,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5126,10 +5131,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306029</v>
+        <v>306218</v>
       </c>
       <c r="R41" t="n">
-        <v>6525415</v>
+        <v>6525455</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5162,11 +5167,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5193,10 +5193,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113237047</v>
+        <v>113237048</v>
       </c>
       <c r="B42" t="n">
-        <v>90248</v>
+        <v>78757</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5209,21 +5209,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1588</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306220</v>
+        <v>306201</v>
       </c>
       <c r="R42" t="n">
-        <v>6525488</v>
+        <v>6525441</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -4046,10 +4046,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113237055</v>
+        <v>113237047</v>
       </c>
       <c r="B31" t="n">
-        <v>56789</v>
+        <v>90254</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>1588</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306208</v>
+        <v>306220</v>
       </c>
       <c r="R31" t="n">
-        <v>6525440</v>
+        <v>6525488</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4122,11 +4122,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4153,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113237063</v>
+        <v>113237046</v>
       </c>
       <c r="B32" t="n">
-        <v>91373</v>
+        <v>90254</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4169,21 +4164,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>1588</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4193,10 +4188,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306029</v>
+        <v>306234</v>
       </c>
       <c r="R32" t="n">
-        <v>6525415</v>
+        <v>6525467</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4229,11 +4224,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4260,10 +4250,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113237054</v>
+        <v>113237057</v>
       </c>
       <c r="B33" t="n">
-        <v>56773</v>
+        <v>56789</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4276,16 +4266,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4300,10 +4290,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306149</v>
+        <v>306222</v>
       </c>
       <c r="R33" t="n">
-        <v>6525175</v>
+        <v>6525470</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4340,7 +4330,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4367,10 +4357,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113237061</v>
+        <v>113237054</v>
       </c>
       <c r="B34" t="n">
-        <v>96321</v>
+        <v>56773</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4379,25 +4369,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4407,10 +4397,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306100</v>
+        <v>306149</v>
       </c>
       <c r="R34" t="n">
-        <v>6525128</v>
+        <v>6525175</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4443,6 +4433,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4469,10 +4464,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113237046</v>
+        <v>113237048</v>
       </c>
       <c r="B35" t="n">
-        <v>90254</v>
+        <v>78757</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4485,21 +4480,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1588</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4509,10 +4504,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306234</v>
+        <v>306201</v>
       </c>
       <c r="R35" t="n">
-        <v>6525467</v>
+        <v>6525441</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4571,10 +4566,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113237047</v>
+        <v>113237049</v>
       </c>
       <c r="B36" t="n">
-        <v>90254</v>
+        <v>78757</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4587,21 +4582,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1588</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306220</v>
+        <v>306210</v>
       </c>
       <c r="R36" t="n">
-        <v>6525488</v>
+        <v>6525458</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4673,10 +4668,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113237049</v>
+        <v>113237065</v>
       </c>
       <c r="B37" t="n">
-        <v>78757</v>
+        <v>91350</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4685,25 +4680,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4713,10 +4708,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306210</v>
+        <v>306104</v>
       </c>
       <c r="R37" t="n">
-        <v>6525458</v>
+        <v>6525382</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4749,6 +4744,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4775,10 +4775,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113237051</v>
+        <v>113237063</v>
       </c>
       <c r="B38" t="n">
-        <v>78757</v>
+        <v>91373</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4791,21 +4791,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306130</v>
+        <v>306029</v>
       </c>
       <c r="R38" t="n">
-        <v>6525370</v>
+        <v>6525415</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4851,6 +4851,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4877,10 +4882,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113237065</v>
+        <v>113237061</v>
       </c>
       <c r="B39" t="n">
-        <v>91350</v>
+        <v>96321</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4893,21 +4898,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4917,10 +4922,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306104</v>
+        <v>306100</v>
       </c>
       <c r="R39" t="n">
-        <v>6525382</v>
+        <v>6525128</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4953,11 +4958,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4984,10 +4984,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113237057</v>
+        <v>113237050</v>
       </c>
       <c r="B40" t="n">
-        <v>56789</v>
+        <v>78757</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5000,21 +5000,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306222</v>
+        <v>306218</v>
       </c>
       <c r="R40" t="n">
-        <v>6525470</v>
+        <v>6525455</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5060,11 +5060,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5091,7 +5086,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113237050</v>
+        <v>113237051</v>
       </c>
       <c r="B41" t="n">
         <v>78757</v>
@@ -5131,10 +5126,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306218</v>
+        <v>306130</v>
       </c>
       <c r="R41" t="n">
-        <v>6525455</v>
+        <v>6525370</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5193,10 +5188,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113237048</v>
+        <v>113237055</v>
       </c>
       <c r="B42" t="n">
-        <v>78757</v>
+        <v>56789</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5209,21 +5204,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5233,10 +5228,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306201</v>
+        <v>306208</v>
       </c>
       <c r="R42" t="n">
-        <v>6525441</v>
+        <v>6525440</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5269,6 +5264,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -4046,10 +4046,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113237047</v>
+        <v>113237046</v>
       </c>
       <c r="B31" t="n">
-        <v>90254</v>
+        <v>90261</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306220</v>
+        <v>306234</v>
       </c>
       <c r="R31" t="n">
-        <v>6525488</v>
+        <v>6525467</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113237046</v>
+        <v>113237048</v>
       </c>
       <c r="B32" t="n">
-        <v>90254</v>
+        <v>78764</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4164,21 +4164,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1588</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306234</v>
+        <v>306201</v>
       </c>
       <c r="R32" t="n">
-        <v>6525467</v>
+        <v>6525441</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113237057</v>
+        <v>113237055</v>
       </c>
       <c r="B33" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306222</v>
+        <v>306208</v>
       </c>
       <c r="R33" t="n">
-        <v>6525470</v>
+        <v>6525440</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4357,10 +4357,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113237054</v>
+        <v>113237049</v>
       </c>
       <c r="B34" t="n">
-        <v>56773</v>
+        <v>78764</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4373,21 +4373,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306149</v>
+        <v>306210</v>
       </c>
       <c r="R34" t="n">
-        <v>6525175</v>
+        <v>6525458</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4433,11 +4433,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4464,10 +4459,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113237048</v>
+        <v>113237054</v>
       </c>
       <c r="B35" t="n">
-        <v>78757</v>
+        <v>56780</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4480,21 +4475,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4504,10 +4499,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306201</v>
+        <v>306149</v>
       </c>
       <c r="R35" t="n">
-        <v>6525441</v>
+        <v>6525175</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4540,6 +4535,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4566,10 +4566,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113237049</v>
+        <v>113237063</v>
       </c>
       <c r="B36" t="n">
-        <v>78757</v>
+        <v>91380</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4582,21 +4582,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306210</v>
+        <v>306029</v>
       </c>
       <c r="R36" t="n">
-        <v>6525458</v>
+        <v>6525415</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4642,6 +4642,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4668,10 +4673,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113237065</v>
+        <v>113237047</v>
       </c>
       <c r="B37" t="n">
-        <v>91350</v>
+        <v>90261</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4680,25 +4685,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>1588</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4708,10 +4713,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306104</v>
+        <v>306220</v>
       </c>
       <c r="R37" t="n">
-        <v>6525382</v>
+        <v>6525488</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4744,11 +4749,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4775,10 +4775,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113237063</v>
+        <v>113237051</v>
       </c>
       <c r="B38" t="n">
-        <v>91373</v>
+        <v>78764</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4791,21 +4791,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306029</v>
+        <v>306130</v>
       </c>
       <c r="R38" t="n">
-        <v>6525415</v>
+        <v>6525370</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4851,11 +4851,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4885,7 +4880,7 @@
         <v>113237061</v>
       </c>
       <c r="B39" t="n">
-        <v>96321</v>
+        <v>96328</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4987,7 +4982,7 @@
         <v>113237050</v>
       </c>
       <c r="B40" t="n">
-        <v>78757</v>
+        <v>78764</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5086,10 +5081,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113237051</v>
+        <v>113237057</v>
       </c>
       <c r="B41" t="n">
-        <v>78757</v>
+        <v>56796</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5102,21 +5097,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5126,10 +5121,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306130</v>
+        <v>306222</v>
       </c>
       <c r="R41" t="n">
-        <v>6525370</v>
+        <v>6525470</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5162,6 +5157,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5188,10 +5188,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113237055</v>
+        <v>113237065</v>
       </c>
       <c r="B42" t="n">
-        <v>56789</v>
+        <v>91357</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5200,25 +5200,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306208</v>
+        <v>306104</v>
       </c>
       <c r="R42" t="n">
-        <v>6525440</v>
+        <v>6525382</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>5 fruktkroppar</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42296-2019 artfynd.xlsx
+++ b/artfynd/A 42296-2019 artfynd.xlsx
@@ -5150,7 +5150,7 @@
         <v>127047207</v>
       </c>
       <c r="B41" t="n">
-        <v>89979</v>
+        <v>90100</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>127047208</v>
       </c>
       <c r="B42" t="n">
-        <v>91664</v>
+        <v>91738</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
